--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104503_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104503_W5.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7488</v>
+        <v>3.1651</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3506</v>
+        <v>1.4486</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6017</v>
+        <v>1.7166</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6318</v>
+        <v>2.9014</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4719</v>
+        <v>0.3564</v>
       </c>
       <c r="I2" t="n">
-        <v>0.16</v>
+        <v>2.545</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5694</v>
+        <v>2.3676</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6467</v>
+        <v>0.5441</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.07729999999999999</v>
+        <v>1.8235</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0625</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1749</v>
+        <v>-0.1877</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2373</v>
+        <v>0.7215</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2268</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9148</v>
+        <v>0.4019</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5939</v>
+        <v>0.8126</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3209</v>
+        <v>-0.4107</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.0246</v>
+        <v>0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3214</v>
+        <v>0.5447</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.3461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.963</v>
+        <v>2.5343</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0385</v>
+        <v>3.4425</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9245</v>
+        <v>-0.9082</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3485</v>
+        <v>3.6297</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2135</v>
+        <v>3.4642</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1351</v>
+        <v>0.1656</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4811</v>
+        <v>3.5409</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7029</v>
+        <v>3.623</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7782</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4894</v>
+        <v>-0.1588</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3568</v>
+        <v>0.2477</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6825</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>1.733</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0505</v>
+        <v>-0.0262</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1607</v>
+        <v>-2.0212</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>0.3155</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2534</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6254</v>
+        <v>2.4288</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5053</v>
+        <v>1.2125</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1201</v>
+        <v>1.2162</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9222</v>
+        <v>2.047</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3608</v>
+        <v>1.1572</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5614</v>
+        <v>0.8897</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4198</v>
+        <v>1.7147</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5675</v>
+        <v>1.603</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8523</v>
+        <v>0.1117</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.3322</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2066</v>
+        <v>-0.4458</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7091</v>
+        <v>0.778</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1627</v>
+        <v>0.8582</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8075</v>
+        <v>0.4782</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9703000000000001</v>
+        <v>0.3801</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5463</v>
+        <v>-0.9317</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>H. DIALLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.523</v>
+        <v>2.377</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5565</v>
+        <v>0.9498</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9665</v>
+        <v>1.4273</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0326</v>
+        <v>1.6043</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1529</v>
+        <v>0.5926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8797</v>
+        <v>1.0118</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7224</v>
+        <v>1.689</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6105</v>
+        <v>1.7712</v>
       </c>
       <c r="L5" t="n">
-        <v>0.112</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3102</v>
+        <v>-0.0847</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4576</v>
+        <v>-1.1786</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7678</v>
+        <v>1.0939</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9687</v>
+        <v>-0.1378</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8075</v>
+        <v>0.0834</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1612</v>
+        <v>-0.2212</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0.3155</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. DIALLO</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3844</v>
+        <v>2.1163</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1519</v>
+        <v>1.2547</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2325</v>
+        <v>0.8616</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6142</v>
+        <v>2.3495</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6092</v>
+        <v>0.218</v>
       </c>
       <c r="I6" t="n">
-        <v>1.005</v>
+        <v>2.1315</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7298</v>
+        <v>1.4594</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8072</v>
+        <v>0.6927</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1157</v>
+        <v>0.8901</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.198</v>
+        <v>-0.4747</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0823</v>
+        <v>1.3648</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.137</v>
+        <v>0.8351</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7652</v>
+        <v>0.9822</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6281</v>
+        <v>-0.1471</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3214</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3214</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3141</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1038</v>
+        <v>-0.7995</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2103</v>
+        <v>1.6982</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6897</v>
+        <v>-0.3442</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.596</v>
+        <v>0.204</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9063</v>
+        <v>-0.5483</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2403</v>
+        <v>-0.1581</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9493</v>
+        <v>1.5406</v>
       </c>
       <c r="L7" t="n">
-        <v>0.709</v>
+        <v>-1.6987</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4494</v>
+        <v>-0.1861</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-1.3365</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1973</v>
+        <v>1.1504</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7543</v>
+        <v>0.5389</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2249</v>
+        <v>0.5454</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4706</v>
+        <v>-0.0066</v>
       </c>
       <c r="V7" t="n">
-        <v>1.7032</v>
+        <v>0.9317</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4498</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1955</v>
+        <v>0.6856</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0173</v>
+        <v>0.2595</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1781</v>
+        <v>0.4261</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1746</v>
+        <v>-0.6811</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1746</v>
+        <v>-1.5914</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.9103</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0173</v>
+        <v>-0.2513</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0173</v>
+        <v>-0.9588</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.7075</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1573</v>
+        <v>-0.4298</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1573</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.2028</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0209</v>
+        <v>0.1163</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.4016</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0209</v>
+        <v>-0.2854</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.7057</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.4584</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1104</v>
+        <v>0.4643</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4889</v>
+        <v>0.2541</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5993</v>
+        <v>0.2102</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3401</v>
+        <v>0.1752</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2064</v>
+        <v>0.1752</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5464</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1258</v>
+        <v>0.0172</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5616</v>
+        <v>0.0172</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.6874</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2143</v>
+        <v>0.1579</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3552</v>
+        <v>0.1579</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1409</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0415</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2547</v>
+        <v>0.2892</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1875</v>
+        <v>0.2369</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0672</v>
+        <v>0.0523</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4279</v>
+        <v>-0.9532</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5342</v>
+        <v>-1.1628</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1064</v>
+        <v>0.2096</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0885</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.5432</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8266</v>
+        <v>-0.3589</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4174</v>
+        <v>-0.0419</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4092</v>
+        <v>-0.317</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5958</v>
+        <v>-1.2168</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5679</v>
+        <v>-2.2427</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9722</v>
+        <v>1.026</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0438</v>
+        <v>2.0431</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1588</v>
+        <v>1.1521</v>
       </c>
       <c r="I11" t="n">
-        <v>0.885</v>
+        <v>0.8911</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1824</v>
+        <v>1.1649</v>
       </c>
       <c r="K11" t="n">
-        <v>0.436</v>
+        <v>0.4202</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.8782</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7228</v>
+        <v>0.7319</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4019</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3478</v>
+        <v>0.0068</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7497</v>
+        <v>0.782</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.1491</v>
+        <v>-5.1164</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5996</v>
+        <v>-2.6943</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5495</v>
+        <v>-2.4221</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2519</v>
+        <v>-0.2531</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4861</v>
+        <v>1.4931</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.738</v>
+        <v>-1.7462</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5779</v>
+        <v>-0.5998</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2988</v>
+        <v>1.2928</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8767</v>
+        <v>-1.8925</v>
       </c>
       <c r="M12" t="n">
-        <v>0.326</v>
+        <v>0.3467</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4455</v>
+        <v>0.5936</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4869</v>
+        <v>0.4596</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0414</v>
+        <v>0.1339</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.9566</v>
+        <v>-2.9529</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.8243</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.691800000000002</v>
+        <v>7.383699999999997</v>
       </c>
       <c r="E13" t="n">
-        <v>1.533300000000001</v>
+        <v>1.9224</v>
       </c>
       <c r="F13" t="n">
-        <v>5.1587</v>
+        <v>5.461499999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>13.5652</v>
+        <v>13.5603</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6883</v>
+        <v>6.678199999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>6.8772</v>
+        <v>6.882200000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>11.1955</v>
+        <v>10.9617</v>
       </c>
       <c r="K13" t="n">
-        <v>10.7165</v>
+        <v>10.5632</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4790999999999999</v>
+        <v>0.3985999999999996</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3698</v>
+        <v>2.5985</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.028099999999999</v>
+        <v>-3.885</v>
       </c>
       <c r="O13" t="n">
-        <v>6.398000000000001</v>
+        <v>6.4834</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.805</v>
+        <v>-6.8289</v>
       </c>
       <c r="Q13" t="n">
-        <v>-19.2809</v>
+        <v>-19.3489</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S13" t="n">
-        <v>3.9166</v>
+        <v>4.6234</v>
       </c>
       <c r="T13" t="n">
-        <v>3.962</v>
+        <v>4.6891</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.04559999999999997</v>
+        <v>-0.06589999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.985099999999999</v>
+        <v>-3.971</v>
       </c>
       <c r="W13" t="n">
-        <v>5.656400000000001</v>
+        <v>5.619999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.641500000000001</v>
+        <v>-9.591000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9642</v>
+        <v>6.9254</v>
       </c>
       <c r="E14" t="n">
-        <v>7.0814</v>
+        <v>6.8181</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1172</v>
+        <v>0.1073</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4121</v>
+        <v>2.4234</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8469</v>
+        <v>1.8495</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5652</v>
+        <v>0.5739</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9909</v>
+        <v>3.9728</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8789</v>
+        <v>3.8611</v>
       </c>
       <c r="L14" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5788</v>
+        <v>-1.5494</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.032</v>
+        <v>-2.0116</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P14" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6067</v>
+        <v>-0.6573</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0393</v>
+        <v>-0.1955</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.646</v>
+        <v>-0.4618</v>
       </c>
       <c r="V14" t="n">
-        <v>3.1173</v>
+        <v>3.1107</v>
       </c>
       <c r="W14" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7766</v>
+        <v>4.4247</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6056</v>
+        <v>4.2311</v>
       </c>
       <c r="F15" t="n">
-        <v>0.171</v>
+        <v>0.1936</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7089</v>
+        <v>1.7072</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3406</v>
+        <v>2.3326</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6317</v>
+        <v>-0.6254</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5265</v>
+        <v>2.5081</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4519</v>
+        <v>2.4336</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8176</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3871</v>
+        <v>0.0346</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8257</v>
+        <v>0.4757</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4386</v>
+        <v>-0.4411</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2436</v>
+        <v>2.2825</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4368</v>
+        <v>0.2842</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8067</v>
+        <v>1.9984</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.707</v>
+        <v>-1.7039</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2149</v>
+        <v>0.2208</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.9219</v>
+        <v>-1.9247</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6208</v>
+        <v>-0.644</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0665</v>
+        <v>1.0547</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.6874</v>
+        <v>-1.6987</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0861</v>
+        <v>-1.0599</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8516</v>
+        <v>-0.8339</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3342</v>
+        <v>0.375</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8438</v>
+        <v>0.7311</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.3562</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5748</v>
+        <v>1.5628</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5748</v>
+        <v>1.5628</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6021</v>
+        <v>0.9998</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7139</v>
+        <v>1.0565</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1118</v>
+        <v>-0.0568</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2138</v>
+        <v>0.2237</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1834</v>
+        <v>-0.1756</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3972</v>
+        <v>0.3993</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3399</v>
+        <v>1.3285</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4546</v>
+        <v>1.4479</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1147</v>
+        <v>-0.1194</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1261</v>
+        <v>-1.1048</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.638</v>
+        <v>-1.6235</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3583</v>
+        <v>-0.9767</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6261</v>
+        <v>-0.272</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7322</v>
+        <v>-0.7047</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>B. FITIPALDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1816</v>
+        <v>-2.1584</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.129</v>
+        <v>-2.1953</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0527</v>
+        <v>0.037</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.3407</v>
+        <v>-1.2362</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.5436</v>
+        <v>0.2609</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7971</v>
+        <v>-1.4971</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.181</v>
+        <v>-0.3182</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7944</v>
+        <v>1.2238</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3867</v>
+        <v>-1.542</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1596</v>
+        <v>-0.918</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7493</v>
+        <v>-0.9629</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4104</v>
+        <v>0.0449</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.6293</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9488</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1851</v>
+        <v>-0.3578</v>
       </c>
       <c r="T18" t="n">
-        <v>0.496</v>
+        <v>-0.5113</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6811</v>
+        <v>0.1535</v>
       </c>
       <c r="V18" t="n">
-        <v>2.0246</v>
+        <v>-1.2472</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. FITIPALDO</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5339</v>
+        <v>-2.4684</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4139</v>
+        <v>-2.2119</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.12</v>
+        <v>-0.2566</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.243</v>
+        <v>-3.37</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2524</v>
+        <v>-2.5637</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4954</v>
+        <v>-0.8063</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3059</v>
+        <v>-1.2498</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2295</v>
+        <v>-0.8391</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.5354</v>
+        <v>-0.4107</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9371</v>
+        <v>-2.1202</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9771</v>
+        <v>-1.7246</v>
       </c>
       <c r="O19" t="n">
-        <v>0.04</v>
+        <v>-0.3956</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>-3.6421</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>2.9592</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.718</v>
+        <v>-0.4367</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.747</v>
+        <v>0.5011</v>
       </c>
       <c r="U19" t="n">
-        <v>0.029</v>
+        <v>-0.9378</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2534</v>
+        <v>2.0212</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7124</v>
+        <v>-3.3533</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.296</v>
+        <v>-2.7817</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4164</v>
+        <v>-0.5717</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2563</v>
+        <v>-3.2449</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.9018</v>
+        <v>-2.8981</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3545</v>
+        <v>-0.3467</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.0042</v>
+        <v>-3.0179</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.2552</v>
+        <v>-2.2655</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2521</v>
+        <v>-0.227</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2075</v>
+        <v>-0.4531</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5474</v>
+        <v>0.0785</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.34</v>
+        <v>-0.5315</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="21">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6138</v>
+        <v>-3.5718</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.427</v>
+        <v>-5.3436</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8132</v>
+        <v>1.7718</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.7544</v>
+        <v>-3.7619</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.6722</v>
+        <v>-2.682</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0822</v>
+        <v>-1.0799</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.584</v>
+        <v>-4.6112</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.0486</v>
+        <v>-3.0691</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8297</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3764</v>
+        <v>0.3871</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4077</v>
+        <v>-0.3531</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0302</v>
+        <v>0.0902</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3775</v>
+        <v>-0.4433</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.266</v>
+        <v>-3.8917</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9848</v>
+        <v>-3.5494</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2812</v>
+        <v>-0.3423</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9649</v>
+        <v>-1.9652</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7174</v>
+        <v>-0.7044</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2476</v>
+        <v>-1.2608</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0221</v>
+        <v>0.0002</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7793</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7572</v>
+        <v>-0.7754</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.987</v>
+        <v>-1.9654</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4966</v>
+        <v>-1.48</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5526</v>
+        <v>-0.1754</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5383</v>
+        <v>-0.0653</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0142</v>
+        <v>-0.11</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.9706</v>
+        <v>-5.8755</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4526</v>
+        <v>-2.472</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.518</v>
+        <v>-3.4036</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6339</v>
+        <v>-2.6327</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.3247</v>
+        <v>-2.3181</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3092</v>
+        <v>-0.3145</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5532</v>
+        <v>-0.5671</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1812</v>
+        <v>0.1708</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0807</v>
+        <v>-2.0656</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5903</v>
+        <v>-1.5802</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0171</v>
+        <v>-0.9258</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7652</v>
+        <v>-0.7667</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2519</v>
+        <v>-0.159</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.6918</v>
+        <v>-6.686699999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.865599999999997</v>
+        <v>-6.164</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8264</v>
+        <v>-0.5228999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-13.5654</v>
+        <v>-13.5605</v>
       </c>
       <c r="H24" t="n">
-        <v>-6.6883</v>
+        <v>-6.678099999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-6.8772</v>
+        <v>-6.8822</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.369699999999999</v>
+        <v>-2.598600000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>4.028100000000001</v>
+        <v>3.8852</v>
       </c>
       <c r="L24" t="n">
-        <v>-6.398000000000001</v>
+        <v>-6.4836</v>
       </c>
       <c r="M24" t="n">
-        <v>-11.1954</v>
+        <v>-10.9619</v>
       </c>
       <c r="N24" t="n">
-        <v>-10.7165</v>
+        <v>-10.5633</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4792</v>
+        <v>-0.3985</v>
       </c>
       <c r="P24" t="n">
-        <v>6.805</v>
+        <v>6.829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-12.4758</v>
+        <v>-12.5198</v>
       </c>
       <c r="R24" t="n">
-        <v>19.2808</v>
+        <v>19.3488</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.9167</v>
+        <v>-3.926299999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0454</v>
+        <v>0.06579999999999986</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.9621</v>
+        <v>-3.9919</v>
       </c>
       <c r="V24" t="n">
-        <v>3.984999999999999</v>
+        <v>3.9711</v>
       </c>
       <c r="W24" t="n">
-        <v>8.934299999999999</v>
+        <v>8.888400000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.9493</v>
+        <v>-4.9175</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104503_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104503_W5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.4584</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-9.591000000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104503_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-4.9175</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
